--- a/results/Int All Data -0.4/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_3_permute.xlsx
@@ -440,607 +440,607 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8667298975123434</v>
+        <v>0.8733825579501753</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8667298975123434</v>
+        <v>0.8733825579501753</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8649324712463695</v>
+        <v>0.8730992718311952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8652157573653496</v>
+        <v>0.874613411978189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8693120424338626</v>
+        <v>0.8758442660062026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8654240612456356</v>
+        <v>0.8748966980971691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.88004130286561</v>
+        <v>0.8757465564541096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8817508621167898</v>
+        <v>0.8765964148110501</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8840633215163234</v>
+        <v>0.8976936250780692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8837474655466455</v>
+        <v>0.8973679265710927</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8827998976376121</v>
+        <v>0.8983806341815215</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8822333253996517</v>
+        <v>0.8947759391122747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8854797521112243</v>
+        <v>0.8942093668743144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8854797521112243</v>
+        <v>0.8904387803127779</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8814455645053052</v>
+        <v>0.8904387803127779</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8802147104772915</v>
+        <v>0.8937503467257457</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8761184254087784</v>
+        <v>0.8999599140299106</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8840246671880229</v>
+        <v>0.8911159468789314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8851123570371457</v>
+        <v>0.8892306535981632</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8906250727005596</v>
+        <v>0.8929429007568017</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8921293703102546</v>
+        <v>0.8860592091252848</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8951705353803425</v>
+        <v>0.8879248173314555</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8979284143314501</v>
+        <v>0.8879248173314555</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.901239980744418</v>
+        <v>0.88757639151108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9105202407305668</v>
+        <v>0.886977249422422</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9010544041775308</v>
+        <v>0.887478681958987</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8982995674652245</v>
+        <v>0.8904615076261768</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8902372767309892</v>
+        <v>0.8904615076261768</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8889738528522778</v>
+        <v>0.8981397604505377</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8714101134755072</v>
+        <v>0.8915916098632961</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8750701057088506</v>
+        <v>0.8915916098632961</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.871419956012806</v>
+        <v>0.8397472078511236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8702080712384954</v>
+        <v>0.835400206514328</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8722562137727519</v>
+        <v>0.834996483529856</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8691302239266714</v>
+        <v>0.8347556097988722</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8633372643830788</v>
+        <v>0.8298942911494115</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8626207276677302</v>
+        <v>0.8298942911494115</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8714290827292104</v>
+        <v>0.8298942911494115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8727121916825191</v>
+        <v>0.8064337981993526</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8726470519811238</v>
+        <v>0.8000484968655992</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8725819122797285</v>
+        <v>0.803054049846188</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8716669142213926</v>
+        <v>0.7950372137387505</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8633871928904668</v>
+        <v>0.8032070565623776</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8614594872217023</v>
+        <v>0.8003741953725758</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8673433560188906</v>
+        <v>0.7999606298508051</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8577373975257651</v>
+        <v>0.7906121879244594</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8577373975257651</v>
+        <v>0.7914067491173034</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.859655260657231</v>
+        <v>0.7935851710543504</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8585221161813104</v>
+        <v>0.7815992870423891</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8547644143958739</v>
+        <v>0.7809024354016382</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8473694476904934</v>
+        <v>0.7809024354016382</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8608535448345469</v>
+        <v>0.7815568746543927</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8619965318477665</v>
+        <v>0.7580994239431351</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8533123717114741</v>
+        <v>0.755517279021616</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8412257359086184</v>
+        <v>0.7656928519915032</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8340814854715202</v>
+        <v>0.7663798610949555</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8320659127879613</v>
+        <v>0.7752071854101386</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8393169994935568</v>
+        <v>0.7696944697467247</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8262427098115781</v>
+        <v>0.7568231152883237</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8315569641320045</v>
+        <v>0.7592749808070522</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8338883927852412</v>
+        <v>0.7662919940801611</v>
       </c>
     </row>
     <row r="63">
@@ -1050,217 +1050,217 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8327878181600181</v>
+        <v>0.7662919940801611</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8330711042789983</v>
+        <v>0.7674902782574772</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8330711042789983</v>
+        <v>0.7609746975209333</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8356434066632188</v>
+        <v>0.7609746975209333</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8356434066632188</v>
+        <v>0.7549832766343534</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8367863936764381</v>
+        <v>0.7558657048419914</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8358388257674048</v>
+        <v>0.7591318166281614</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.842494528444038</v>
+        <v>0.7581516788684304</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.842494528444038</v>
+        <v>0.7596006793140289</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8422112423250578</v>
+        <v>0.7681644025848293</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8428656815778124</v>
+        <v>0.7590992467774638</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8453273896338398</v>
+        <v>0.7596658190154242</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8349207854702675</v>
+        <v>0.8138545344569336</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8203785260889873</v>
+        <v>0.8131349555027837</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8165882544528533</v>
+        <v>0.7884496930023139</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8184280931068237</v>
+        <v>0.7953788392606286</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8260480065282866</v>
+        <v>0.7933503818009695</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8263312926472668</v>
+        <v>0.7971959506012001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8406554056109621</v>
+        <v>0.795899956871791</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8460673694834815</v>
+        <v>0.7930019559805941</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8292323357772652</v>
+        <v>0.7943108344861032</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8277181956302713</v>
+        <v>0.7940926880685184</v>
       </c>
     </row>
     <row r="85">
@@ -1270,717 +1270,717 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8293853424934547</v>
+        <v>0.7946592603064787</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8329150553240074</v>
+        <v>0.7943759741874985</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.829645901299036</v>
+        <v>0.7647801803510743</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8296330165229358</v>
+        <v>0.7609247690135451</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8262759954831702</v>
+        <v>0.7609346115508439</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8129418628165046</v>
+        <v>0.7404759135216777</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8175266956454825</v>
+        <v>0.7396260551647372</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8175266956454825</v>
+        <v>0.7338527806957421</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8175819928095791</v>
+        <v>0.7269751735418282</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8127237163989198</v>
+        <v>0.7201695063878066</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8159080456478984</v>
+        <v>0.729683839806442</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8151884666937486</v>
+        <v>0.7312305498041335</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8158201786331042</v>
+        <v>0.7278992983165682</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8110270419238402</v>
+        <v>0.7303610063725956</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8110270419238402</v>
+        <v>0.7194302423590593</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8043516541726095</v>
+        <v>0.7130805531148052</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7736545698900679</v>
+        <v>0.7206088414617778</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7787930901809059</v>
+        <v>0.7070239925268298</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7927331652347266</v>
+        <v>0.7043441380532177</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7943351723965146</v>
+        <v>0.7083555983457379</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7943351723965146</v>
+        <v>0.7098174835674367</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7694734600455619</v>
+        <v>0.7139690658000462</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7630260612492148</v>
+        <v>0.6983981717934356</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7787408352556107</v>
+        <v>0.7068088883480463</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6958949461255299</v>
+        <v>0.7127351695332311</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6958949461255299</v>
+        <v>0.7154475938575409</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7237849387704702</v>
+        <v>0.6930248622492166</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7207400156406865</v>
+        <v>0.6999336076120394</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7128178468465405</v>
+        <v>0.6264102119008803</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7077088541675987</v>
+        <v>0.6476044158990979</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6725412894439682</v>
+        <v>0.6293506251800737</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7111279726699582</v>
+        <v>0.643580786651372</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7173140968398297</v>
+        <v>0.6192833201204726</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7112802635652533</v>
+        <v>0.5724215683993708</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7094828372992794</v>
+        <v>0.5724215683993708</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7132927940100108</v>
+        <v>0.4862927456921003</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7198250175823507</v>
+        <v>0.5103228531189211</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7161059701252149</v>
+        <v>0.5213778120576451</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6983430535845626</v>
+        <v>0.5701833754176368</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.701110775072969</v>
+        <v>0.5504548147008137</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7024393386530756</v>
+        <v>0.5454336890366661</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6888568161360346</v>
+        <v>0.5430371206820341</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6859815425582365</v>
+        <v>0.5372767309891393</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6861996889758213</v>
+        <v>0.5384356450172603</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6516933638034428</v>
+        <v>0.5264928892141898</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6627483227421667</v>
+        <v>0.587428216585928</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6664052727367085</v>
+        <v>0.6066417441691914</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.667255131093649</v>
+        <v>0.6013767025352587</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6677565636302141</v>
+        <v>0.6013767025352587</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6660409199014314</v>
+        <v>0.6006374385065113</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6315770071170492</v>
+        <v>0.600670008357209</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4660901325879252</v>
+        <v>0.587087485840168</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4623293885636874</v>
+        <v>0.587087485840168</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4591708288669092</v>
+        <v>0.587087485840168</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4591708288669092</v>
+        <v>0.5867716298704901</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4398059051644688</v>
+        <v>0.5968047544823809</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4534165236516171</v>
+        <v>0.5380965248685127</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4128869235628554</v>
+        <v>0.5619129597583389</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4183314572860725</v>
+        <v>0.5658107834838645</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4152054674399919</v>
+        <v>0.559552003493206</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4152054674399919</v>
+        <v>0.559552003493206</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3541271548445863</v>
+        <v>0.5557261197675729</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4100687367013899</v>
+        <v>0.5531697443982542</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4024949937276194</v>
+        <v>0.5269400983179998</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4716585033258828</v>
+        <v>0.5338964457703038</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4716585033258828</v>
+        <v>0.5099670901343775</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4954219674695194</v>
+        <v>0.5097163738660949</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4935268316514524</v>
+        <v>0.5086582116288684</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4920225340417574</v>
+        <v>0.5020411632805355</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4989319952254746</v>
+        <v>0.4953240789622029</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5008597008942393</v>
+        <v>0.4954241149322028</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4998795631345081</v>
+        <v>0.4994484600008232</v>
       </c>
     </row>
   </sheetData>
